--- a/data/trans_dic/P70B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P70B_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que concilia su vida profesional y laboral</t>
+          <t>Población que concilia su vida profesional y laboral (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,7; 98,48</t>
+          <t>91,33; 98,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,97; 97,58</t>
+          <t>91,34; 97,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,16; 97,67</t>
+          <t>92,93; 97,74</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,34; 82,89</t>
+          <t>66,69; 82,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,87; 81,88</t>
+          <t>69,35; 81,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,6; 80,71</t>
+          <t>70,2; 80,43</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,94; 78,42</t>
+          <t>62,5; 78,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,91; 80,52</t>
+          <t>65,97; 79,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,04; 77,18</t>
+          <t>67,17; 77,34</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,73; 87,4</t>
+          <t>71,86; 88,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,65; 95,28</t>
+          <t>80,84; 95,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,1; 91,81</t>
+          <t>79,19; 92,05</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,79; 98,22</t>
+          <t>92,11; 98,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,08; 98,92</t>
+          <t>93,69; 98,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,07; 98,01</t>
+          <t>94,05; 98,16</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,59; 78,65</t>
+          <t>63,98; 78,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,33; 82,29</t>
+          <t>65,99; 81,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67,09; 77,99</t>
+          <t>66,31; 77,92</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>80,85; 89,41</t>
+          <t>80,56; 89,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>85,43; 91,22</t>
+          <t>85,1; 91,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84,0; 89,4</t>
+          <t>83,9; 89,25</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>91,89; 98,63</t>
+          <t>92,38; 98,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>79,06; 89,93</t>
+          <t>79,58; 90,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,21; 96,76</t>
+          <t>89,34; 96,92</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>84,17; 90,95</t>
+          <t>84,0; 91,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>83,89; 88,28</t>
+          <t>83,94; 88,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84,78; 89,35</t>
+          <t>84,67; 89,29</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que concilia su vida profesional y laboral</t>
+          <t>Población que concilia su vida profesional y laboral (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>178086; 191250</t>
+          <t>177365; 191337</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>131303; 140841</t>
+          <t>131829; 141226</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>315388; 330639</t>
+          <t>314598; 330893</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>158948; 198623</t>
+          <t>159788; 198380</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>116746; 136813</t>
+          <t>115872; 136899</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>283066; 328246</t>
+          <t>285490; 327090</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>95071; 116604</t>
+          <t>92931; 116536</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80870; 97320</t>
+          <t>79729; 96524</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180712; 208033</t>
+          <t>181056; 208466</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>120856; 147268</t>
+          <t>121087; 149219</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>207891; 245598</t>
+          <t>208377; 244895</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>337199; 391361</t>
+          <t>337563; 392400</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>104234; 111532</t>
+          <t>104593; 111424</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>99699; 105956</t>
+          <t>100359; 105873</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>207584; 216277</t>
+          <t>207536; 216607</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>85880; 106221</t>
+          <t>86419; 106198</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>57306; 71104</t>
+          <t>57019; 70489</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>148573; 172720</t>
+          <t>146863; 172565</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>271242; 299945</t>
+          <t>270273; 299315</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>261731; 279474</t>
+          <t>260731; 278831</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>539189; 573824</t>
+          <t>538542; 572847</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>577364; 619746</t>
+          <t>580423; 621627</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>215041; 244610</t>
+          <t>216467; 244838</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>803156; 871124</t>
+          <t>804400; 872646</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1652582; 1785734</t>
+          <t>1649331; 1795233</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1226398; 1290624</t>
+          <t>1227209; 1292206</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2904039; 3060596</t>
+          <t>2900291; 3058549</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P70B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P70B_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,33; 98,53</t>
+          <t>90,92; 97,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,34; 97,85</t>
+          <t>91,47; 97,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,93; 97,74</t>
+          <t>92,39; 97,02</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,91%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,69; 82,79</t>
+          <t>69,3; 83,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,35; 81,93</t>
+          <t>69,81; 82,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,2; 80,43</t>
+          <t>71,4; 81,65</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,5; 78,38</t>
+          <t>63,78; 78,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,97; 79,86</t>
+          <t>66,49; 80,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,17; 77,34</t>
+          <t>67,15; 77,14</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,86; 88,56</t>
+          <t>71,85; 88,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,84; 95,0</t>
+          <t>74,95; 86,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,19; 92,05</t>
+          <t>75,55; 85,46</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>92,11; 98,12</t>
+          <t>91,26; 97,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,69; 98,84</t>
+          <t>92,63; 98,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,05; 98,16</t>
+          <t>93,53; 97,73</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,9%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,98; 78,63</t>
+          <t>64,31; 77,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65,99; 81,58</t>
+          <t>67,51; 83,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66,31; 77,92</t>
+          <t>67,28; 78,44</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>80,56; 89,22</t>
+          <t>81,72; 89,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>85,1; 91,01</t>
+          <t>84,77; 90,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83,9; 89,25</t>
+          <t>84,53; 89,44</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>92,38; 98,93</t>
+          <t>90,81; 95,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>79,58; 90,01</t>
+          <t>84,53; 91,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,34; 96,92</t>
+          <t>88,97; 93,12</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,52%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>84,0; 91,43</t>
+          <t>83,5; 87,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>83,94; 88,39</t>
+          <t>84,01; 87,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84,67; 89,29</t>
+          <t>84,24; 86,71</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>186853</t>
+          <t>192227</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>137910</t>
+          <t>145563</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>324763</t>
+          <t>337790</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>177365; 191337</t>
+          <t>183942; 197250</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>131829; 141226</t>
+          <t>139732; 148981</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>314598; 330893</t>
+          <t>328038; 344480</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>180575</t>
+          <t>192003</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>127946</t>
+          <t>135235</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>308521</t>
+          <t>327237</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>159788; 198380</t>
+          <t>172884; 208893</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>115872; 136899</t>
+          <t>122850; 145261</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>285490; 327090</t>
+          <t>303778; 347390</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>105633</t>
+          <t>106568</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89282</t>
+          <t>91579</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>194914</t>
+          <t>198147</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92931; 116536</t>
+          <t>95426; 116994</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>79729; 96524</t>
+          <t>81797; 98952</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>181056; 208466</t>
+          <t>183074; 210313</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>136696</t>
+          <t>170573</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>227960</t>
+          <t>145356</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>364655</t>
+          <t>315928</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121087; 149219</t>
+          <t>151601; 186369</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>208377; 244895</t>
+          <t>134354; 154281</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>337563; 392400</t>
+          <t>294822; 333516</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>108892</t>
+          <t>129477</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>104072</t>
+          <t>115553</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>212964</t>
+          <t>245030</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>104593; 111424</t>
+          <t>123585; 132568</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>100359; 105873</t>
+          <t>110644; 118008</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>207536; 216607</t>
+          <t>238387; 249075</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>96924</t>
+          <t>96839</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>64762</t>
+          <t>66044</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161686</t>
+          <t>162884</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>86419; 106198</t>
+          <t>87519; 106077</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>57019; 70489</t>
+          <t>58977; 72690</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>146863; 172565</t>
+          <t>150322; 175256</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>287187</t>
+          <t>334629</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>270857</t>
+          <t>320006</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>558044</t>
+          <t>654635</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>270273; 299315</t>
+          <t>317660; 347993</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>260731; 278831</t>
+          <t>307125; 329364</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>538542; 572847</t>
+          <t>634821; 671711</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>601526</t>
+          <t>425042</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>234879</t>
+          <t>275801</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>836405</t>
+          <t>700844</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>580423; 621627</t>
+          <t>413132; 435987</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>216467; 244838</t>
+          <t>264687; 285807</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>804400; 872646</t>
+          <t>683395; 715270</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1704284</t>
+          <t>1647358</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1257670</t>
+          <t>1295137</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2961954</t>
+          <t>2942495</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1649331; 1795233</t>
+          <t>1609585; 1682397</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1227209; 1292206</t>
+          <t>1271312; 1320028</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2900291; 3058549</t>
+          <t>2898616; 2983553</t>
         </is>
       </c>
     </row>
